--- a/notas.xlsx
+++ b/notas.xlsx
@@ -423,7 +423,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
